--- a/data/BI Views description_.xlsx
+++ b/data/BI Views description_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/korosh/Desktop/ivs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09770470-5B7D-594C-8F7F-F2F428251701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506E3368-053C-E447-A6B4-0BAB8A70CF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" xr2:uid="{D94CA34D-85F2-42FF-8E10-2C521234CEE1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{D94CA34D-85F2-42FF-8E10-2C521234CEE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -171,9 +171,6 @@
     <t>Plan progress of projects by date</t>
   </si>
   <si>
-    <t>This view contains general information on Projects, like Name, Type, Status, location and other cutom fields</t>
-  </si>
-  <si>
     <t>This view provide timed data on aggregated plan and actual progress of projects It is used to create progress charts in projectlevel.</t>
   </si>
   <si>
@@ -190,6 +187,9 @@
   </si>
   <si>
     <t>A historical snapshot table that records each project plan’s WBS hierarchy, names, creation time, and planned start/end dates, stored in both Gregorian and Jalali calendar formats.</t>
+  </si>
+  <si>
+    <t>This view contains general information on Projects, like Name, Type, Status, project's location and other cutom fields</t>
   </si>
 </sst>
 </file>
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -583,7 +583,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -687,7 +687,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
@@ -735,7 +735,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" x14ac:dyDescent="0.2">
@@ -743,7 +743,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="32" x14ac:dyDescent="0.2">
@@ -751,7 +751,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -767,7 +767,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="32" x14ac:dyDescent="0.2">
